--- a/LoanOfficer-A/2023/63 ibeyaima.xlsx
+++ b/LoanOfficer-A/2023/63 ibeyaima.xlsx
@@ -599,7 +599,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -801,7 +801,7 @@
       </c>
       <c r="K1" s="10">
         <f>G1-K2</f>
-        <v>118</v>
+        <v>100</v>
       </c>
       <c r="L1" s="6"/>
       <c r="M1" s="5"/>
@@ -810,7 +810,7 @@
       </c>
       <c r="O1" s="8">
         <f>SUM(C3:C32)+SUM(G3:G32)+SUM(K3:K32)+SUM(O3:O32)</f>
-        <v>200</v>
+        <v>2000</v>
       </c>
       <c r="P1" s="6"/>
     </row>
@@ -834,7 +834,7 @@
       </c>
       <c r="K2" s="9">
         <f>SUM(D3:D32)+SUM(H3:H32)+SUM(L3:L32)+SUM(P3:P32)</f>
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="L2" s="6"/>
       <c r="M2" s="5"/>
@@ -843,7 +843,7 @@
       </c>
       <c r="O2" s="11">
         <f>C2-O1</f>
-        <v>11800</v>
+        <v>10000</v>
       </c>
       <c r="P2" s="6"/>
     </row>
@@ -915,9 +915,15 @@
       <c r="A5" s="1">
         <v>3</v>
       </c>
-      <c r="B5" s="3"/>
-      <c r="C5" s="4"/>
-      <c r="D5" s="1"/>
+      <c r="B5" s="3">
+        <v>45563</v>
+      </c>
+      <c r="C5" s="4">
+        <v>100</v>
+      </c>
+      <c r="D5" s="1">
+        <v>1</v>
+      </c>
       <c r="E5" s="1">
         <v>33</v>
       </c>
@@ -941,9 +947,15 @@
       <c r="A6" s="1">
         <v>4</v>
       </c>
-      <c r="B6" s="3"/>
-      <c r="C6" s="4"/>
-      <c r="D6" s="1"/>
+      <c r="B6" s="3">
+        <v>45564</v>
+      </c>
+      <c r="C6" s="4">
+        <v>100</v>
+      </c>
+      <c r="D6" s="1">
+        <v>1</v>
+      </c>
       <c r="E6" s="1">
         <v>34</v>
       </c>
@@ -967,9 +979,15 @@
       <c r="A7" s="1">
         <v>5</v>
       </c>
-      <c r="B7" s="3"/>
-      <c r="C7" s="4"/>
-      <c r="D7" s="1"/>
+      <c r="B7" s="3">
+        <v>45565</v>
+      </c>
+      <c r="C7" s="4">
+        <v>100</v>
+      </c>
+      <c r="D7" s="1">
+        <v>1</v>
+      </c>
       <c r="E7" s="1">
         <v>35</v>
       </c>
@@ -993,9 +1011,15 @@
       <c r="A8" s="1">
         <v>6</v>
       </c>
-      <c r="B8" s="3"/>
-      <c r="C8" s="4"/>
-      <c r="D8" s="1"/>
+      <c r="B8" s="3">
+        <v>45566</v>
+      </c>
+      <c r="C8" s="4">
+        <v>100</v>
+      </c>
+      <c r="D8" s="1">
+        <v>1</v>
+      </c>
       <c r="E8" s="1">
         <v>36</v>
       </c>
@@ -1019,9 +1043,15 @@
       <c r="A9" s="1">
         <v>7</v>
       </c>
-      <c r="B9" s="3"/>
-      <c r="C9" s="4"/>
-      <c r="D9" s="1"/>
+      <c r="B9" s="3">
+        <v>45567</v>
+      </c>
+      <c r="C9" s="4">
+        <v>100</v>
+      </c>
+      <c r="D9" s="1">
+        <v>1</v>
+      </c>
       <c r="E9" s="1">
         <v>37</v>
       </c>
@@ -1045,9 +1075,15 @@
       <c r="A10" s="1">
         <v>8</v>
       </c>
-      <c r="B10" s="3"/>
-      <c r="C10" s="4"/>
-      <c r="D10" s="1"/>
+      <c r="B10" s="3">
+        <v>45568</v>
+      </c>
+      <c r="C10" s="4">
+        <v>100</v>
+      </c>
+      <c r="D10" s="1">
+        <v>1</v>
+      </c>
       <c r="E10" s="1">
         <v>38</v>
       </c>
@@ -1071,9 +1107,15 @@
       <c r="A11" s="1">
         <v>9</v>
       </c>
-      <c r="B11" s="3"/>
-      <c r="C11" s="4"/>
-      <c r="D11" s="1"/>
+      <c r="B11" s="3">
+        <v>45569</v>
+      </c>
+      <c r="C11" s="4">
+        <v>100</v>
+      </c>
+      <c r="D11" s="1">
+        <v>1</v>
+      </c>
       <c r="E11" s="1">
         <v>39</v>
       </c>
@@ -1097,9 +1139,15 @@
       <c r="A12" s="1">
         <v>10</v>
       </c>
-      <c r="B12" s="3"/>
-      <c r="C12" s="4"/>
-      <c r="D12" s="1"/>
+      <c r="B12" s="3">
+        <v>45570</v>
+      </c>
+      <c r="C12" s="4">
+        <v>100</v>
+      </c>
+      <c r="D12" s="1">
+        <v>1</v>
+      </c>
       <c r="E12" s="1">
         <v>40</v>
       </c>
@@ -1123,9 +1171,15 @@
       <c r="A13" s="1">
         <v>11</v>
       </c>
-      <c r="B13" s="3"/>
-      <c r="C13" s="4"/>
-      <c r="D13" s="1"/>
+      <c r="B13" s="3">
+        <v>45571</v>
+      </c>
+      <c r="C13" s="4">
+        <v>100</v>
+      </c>
+      <c r="D13" s="1">
+        <v>1</v>
+      </c>
       <c r="E13" s="1">
         <v>41</v>
       </c>
@@ -1149,9 +1203,15 @@
       <c r="A14" s="1">
         <v>12</v>
       </c>
-      <c r="B14" s="3"/>
-      <c r="C14" s="4"/>
-      <c r="D14" s="1"/>
+      <c r="B14" s="3">
+        <v>45572</v>
+      </c>
+      <c r="C14" s="4">
+        <v>100</v>
+      </c>
+      <c r="D14" s="1">
+        <v>1</v>
+      </c>
       <c r="E14" s="1">
         <v>42</v>
       </c>
@@ -1175,9 +1235,15 @@
       <c r="A15" s="1">
         <v>13</v>
       </c>
-      <c r="B15" s="3"/>
-      <c r="C15" s="4"/>
-      <c r="D15" s="1"/>
+      <c r="B15" s="3">
+        <v>45573</v>
+      </c>
+      <c r="C15" s="4">
+        <v>100</v>
+      </c>
+      <c r="D15" s="1">
+        <v>1</v>
+      </c>
       <c r="E15" s="1">
         <v>43</v>
       </c>
@@ -1201,9 +1267,15 @@
       <c r="A16" s="1">
         <v>14</v>
       </c>
-      <c r="B16" s="3"/>
-      <c r="C16" s="4"/>
-      <c r="D16" s="1"/>
+      <c r="B16" s="3">
+        <v>45574</v>
+      </c>
+      <c r="C16" s="4">
+        <v>100</v>
+      </c>
+      <c r="D16" s="1">
+        <v>1</v>
+      </c>
       <c r="E16" s="1">
         <v>44</v>
       </c>
@@ -1227,9 +1299,15 @@
       <c r="A17" s="1">
         <v>15</v>
       </c>
-      <c r="B17" s="3"/>
-      <c r="C17" s="4"/>
-      <c r="D17" s="1"/>
+      <c r="B17" s="3">
+        <v>45575</v>
+      </c>
+      <c r="C17" s="4">
+        <v>100</v>
+      </c>
+      <c r="D17" s="1">
+        <v>1</v>
+      </c>
       <c r="E17" s="1">
         <v>45</v>
       </c>
@@ -1253,9 +1331,15 @@
       <c r="A18" s="1">
         <v>16</v>
       </c>
-      <c r="B18" s="3"/>
-      <c r="C18" s="4"/>
-      <c r="D18" s="1"/>
+      <c r="B18" s="3">
+        <v>45576</v>
+      </c>
+      <c r="C18" s="4">
+        <v>100</v>
+      </c>
+      <c r="D18" s="1">
+        <v>1</v>
+      </c>
       <c r="E18" s="1">
         <v>46</v>
       </c>
@@ -1279,9 +1363,15 @@
       <c r="A19" s="1">
         <v>17</v>
       </c>
-      <c r="B19" s="3"/>
-      <c r="C19" s="4"/>
-      <c r="D19" s="1"/>
+      <c r="B19" s="3">
+        <v>45577</v>
+      </c>
+      <c r="C19" s="4">
+        <v>100</v>
+      </c>
+      <c r="D19" s="1">
+        <v>1</v>
+      </c>
       <c r="E19" s="1">
         <v>47</v>
       </c>
@@ -1305,9 +1395,15 @@
       <c r="A20" s="1">
         <v>18</v>
       </c>
-      <c r="B20" s="3"/>
-      <c r="C20" s="4"/>
-      <c r="D20" s="1"/>
+      <c r="B20" s="3">
+        <v>45578</v>
+      </c>
+      <c r="C20" s="4">
+        <v>100</v>
+      </c>
+      <c r="D20" s="1">
+        <v>1</v>
+      </c>
       <c r="E20" s="1">
         <v>48</v>
       </c>
@@ -1331,9 +1427,15 @@
       <c r="A21" s="1">
         <v>19</v>
       </c>
-      <c r="B21" s="3"/>
-      <c r="C21" s="4"/>
-      <c r="D21" s="1"/>
+      <c r="B21" s="3">
+        <v>45579</v>
+      </c>
+      <c r="C21" s="4">
+        <v>100</v>
+      </c>
+      <c r="D21" s="1">
+        <v>1</v>
+      </c>
       <c r="E21" s="1">
         <v>49</v>
       </c>
@@ -1357,9 +1459,15 @@
       <c r="A22" s="1">
         <v>20</v>
       </c>
-      <c r="B22" s="3"/>
-      <c r="C22" s="4"/>
-      <c r="D22" s="1"/>
+      <c r="B22" s="3">
+        <v>45581</v>
+      </c>
+      <c r="C22" s="4">
+        <v>100</v>
+      </c>
+      <c r="D22" s="1">
+        <v>1</v>
+      </c>
       <c r="E22" s="1">
         <v>50</v>
       </c>

--- a/LoanOfficer-A/2023/63 ibeyaima.xlsx
+++ b/LoanOfficer-A/2023/63 ibeyaima.xlsx
@@ -801,7 +801,7 @@
       </c>
       <c r="K1" s="10">
         <f>G1-K2</f>
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="L1" s="6"/>
       <c r="M1" s="5"/>
@@ -810,7 +810,7 @@
       </c>
       <c r="O1" s="8">
         <f>SUM(C3:C32)+SUM(G3:G32)+SUM(K3:K32)+SUM(O3:O32)</f>
-        <v>2000</v>
+        <v>2200</v>
       </c>
       <c r="P1" s="6"/>
     </row>
@@ -834,7 +834,7 @@
       </c>
       <c r="K2" s="9">
         <f>SUM(D3:D32)+SUM(H3:H32)+SUM(L3:L32)+SUM(P3:P32)</f>
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="L2" s="6"/>
       <c r="M2" s="5"/>
@@ -843,7 +843,7 @@
       </c>
       <c r="O2" s="11">
         <f>C2-O1</f>
-        <v>10000</v>
+        <v>9800</v>
       </c>
       <c r="P2" s="6"/>
     </row>
@@ -1491,9 +1491,15 @@
       <c r="A23" s="1">
         <v>21</v>
       </c>
-      <c r="B23" s="3"/>
-      <c r="C23" s="4"/>
-      <c r="D23" s="1"/>
+      <c r="B23" s="3">
+        <v>45582</v>
+      </c>
+      <c r="C23" s="4">
+        <v>100</v>
+      </c>
+      <c r="D23" s="1">
+        <v>1</v>
+      </c>
       <c r="E23" s="1">
         <v>51</v>
       </c>
@@ -1517,9 +1523,15 @@
       <c r="A24" s="1">
         <v>22</v>
       </c>
-      <c r="B24" s="3"/>
-      <c r="C24" s="4"/>
-      <c r="D24" s="1"/>
+      <c r="B24" s="3">
+        <v>45583</v>
+      </c>
+      <c r="C24" s="4">
+        <v>100</v>
+      </c>
+      <c r="D24" s="1">
+        <v>1</v>
+      </c>
       <c r="E24" s="1">
         <v>52</v>
       </c>

--- a/LoanOfficer-A/2023/63 ibeyaima.xlsx
+++ b/LoanOfficer-A/2023/63 ibeyaima.xlsx
@@ -801,7 +801,7 @@
       </c>
       <c r="K1" s="10">
         <f>G1-K2</f>
-        <v>98</v>
+        <v>82</v>
       </c>
       <c r="L1" s="6"/>
       <c r="M1" s="5"/>
@@ -810,7 +810,7 @@
       </c>
       <c r="O1" s="8">
         <f>SUM(C3:C32)+SUM(G3:G32)+SUM(K3:K32)+SUM(O3:O32)</f>
-        <v>2200</v>
+        <v>3800</v>
       </c>
       <c r="P1" s="6"/>
     </row>
@@ -834,7 +834,7 @@
       </c>
       <c r="K2" s="9">
         <f>SUM(D3:D32)+SUM(H3:H32)+SUM(L3:L32)+SUM(P3:P32)</f>
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="L2" s="6"/>
       <c r="M2" s="5"/>
@@ -843,7 +843,7 @@
       </c>
       <c r="O2" s="11">
         <f>C2-O1</f>
-        <v>9800</v>
+        <v>8200</v>
       </c>
       <c r="P2" s="6"/>
     </row>
@@ -863,9 +863,15 @@
       <c r="E3" s="1">
         <v>31</v>
       </c>
-      <c r="F3" s="3"/>
-      <c r="G3" s="4"/>
-      <c r="H3" s="1"/>
+      <c r="F3" s="3">
+        <v>45593</v>
+      </c>
+      <c r="G3" s="4">
+        <v>100</v>
+      </c>
+      <c r="H3" s="1">
+        <v>1</v>
+      </c>
       <c r="I3" s="1">
         <v>61</v>
       </c>
@@ -895,9 +901,15 @@
       <c r="E4" s="1">
         <v>32</v>
       </c>
-      <c r="F4" s="3"/>
-      <c r="G4" s="4"/>
-      <c r="H4" s="1"/>
+      <c r="F4" s="3">
+        <v>45594</v>
+      </c>
+      <c r="G4" s="4">
+        <v>100</v>
+      </c>
+      <c r="H4" s="1">
+        <v>1</v>
+      </c>
       <c r="I4" s="1">
         <v>62</v>
       </c>
@@ -927,9 +939,15 @@
       <c r="E5" s="1">
         <v>33</v>
       </c>
-      <c r="F5" s="3"/>
-      <c r="G5" s="4"/>
-      <c r="H5" s="1"/>
+      <c r="F5" s="3">
+        <v>45595</v>
+      </c>
+      <c r="G5" s="4">
+        <v>100</v>
+      </c>
+      <c r="H5" s="1">
+        <v>1</v>
+      </c>
       <c r="I5" s="1">
         <v>63</v>
       </c>
@@ -959,9 +977,15 @@
       <c r="E6" s="1">
         <v>34</v>
       </c>
-      <c r="F6" s="3"/>
-      <c r="G6" s="4"/>
-      <c r="H6" s="1"/>
+      <c r="F6" s="3">
+        <v>45596</v>
+      </c>
+      <c r="G6" s="4">
+        <v>100</v>
+      </c>
+      <c r="H6" s="1">
+        <v>1</v>
+      </c>
       <c r="I6" s="1">
         <v>64</v>
       </c>
@@ -991,9 +1015,15 @@
       <c r="E7" s="1">
         <v>35</v>
       </c>
-      <c r="F7" s="3"/>
-      <c r="G7" s="4"/>
-      <c r="H7" s="1"/>
+      <c r="F7" s="3">
+        <v>45597</v>
+      </c>
+      <c r="G7" s="4">
+        <v>100</v>
+      </c>
+      <c r="H7" s="1">
+        <v>1</v>
+      </c>
       <c r="I7" s="1">
         <v>65</v>
       </c>
@@ -1023,9 +1053,15 @@
       <c r="E8" s="1">
         <v>36</v>
       </c>
-      <c r="F8" s="3"/>
-      <c r="G8" s="4"/>
-      <c r="H8" s="1"/>
+      <c r="F8" s="3">
+        <v>45598</v>
+      </c>
+      <c r="G8" s="4">
+        <v>100</v>
+      </c>
+      <c r="H8" s="1">
+        <v>1</v>
+      </c>
       <c r="I8" s="1">
         <v>66</v>
       </c>
@@ -1055,9 +1091,15 @@
       <c r="E9" s="1">
         <v>37</v>
       </c>
-      <c r="F9" s="3"/>
-      <c r="G9" s="4"/>
-      <c r="H9" s="1"/>
+      <c r="F9" s="3">
+        <v>45600</v>
+      </c>
+      <c r="G9" s="4">
+        <v>100</v>
+      </c>
+      <c r="H9" s="1">
+        <v>1</v>
+      </c>
       <c r="I9" s="1">
         <v>67</v>
       </c>
@@ -1087,9 +1129,15 @@
       <c r="E10" s="1">
         <v>38</v>
       </c>
-      <c r="F10" s="3"/>
-      <c r="G10" s="4"/>
-      <c r="H10" s="1"/>
+      <c r="F10" s="3">
+        <v>45601</v>
+      </c>
+      <c r="G10" s="4">
+        <v>100</v>
+      </c>
+      <c r="H10" s="1">
+        <v>1</v>
+      </c>
       <c r="I10" s="1">
         <v>68</v>
       </c>
@@ -1555,9 +1603,15 @@
       <c r="A25" s="1">
         <v>23</v>
       </c>
-      <c r="B25" s="3"/>
-      <c r="C25" s="4"/>
-      <c r="D25" s="1"/>
+      <c r="B25" s="3">
+        <v>45584</v>
+      </c>
+      <c r="C25" s="4">
+        <v>100</v>
+      </c>
+      <c r="D25" s="1">
+        <v>1</v>
+      </c>
       <c r="E25" s="1">
         <v>53</v>
       </c>
@@ -1581,9 +1635,15 @@
       <c r="A26" s="1">
         <v>24</v>
       </c>
-      <c r="B26" s="3"/>
-      <c r="C26" s="4"/>
-      <c r="D26" s="1"/>
+      <c r="B26" s="3">
+        <v>45585</v>
+      </c>
+      <c r="C26" s="4">
+        <v>100</v>
+      </c>
+      <c r="D26" s="1">
+        <v>1</v>
+      </c>
       <c r="E26" s="1">
         <v>54</v>
       </c>
@@ -1607,9 +1667,15 @@
       <c r="A27" s="1">
         <v>25</v>
       </c>
-      <c r="B27" s="3"/>
-      <c r="C27" s="4"/>
-      <c r="D27" s="1"/>
+      <c r="B27" s="3">
+        <v>45586</v>
+      </c>
+      <c r="C27" s="4">
+        <v>100</v>
+      </c>
+      <c r="D27" s="1">
+        <v>1</v>
+      </c>
       <c r="E27" s="1">
         <v>55</v>
       </c>
@@ -1633,9 +1699,15 @@
       <c r="A28" s="1">
         <v>26</v>
       </c>
-      <c r="B28" s="3"/>
-      <c r="C28" s="4"/>
-      <c r="D28" s="1"/>
+      <c r="B28" s="3">
+        <v>45587</v>
+      </c>
+      <c r="C28" s="4">
+        <v>100</v>
+      </c>
+      <c r="D28" s="1">
+        <v>1</v>
+      </c>
       <c r="E28" s="1">
         <v>56</v>
       </c>
@@ -1659,9 +1731,15 @@
       <c r="A29" s="1">
         <v>27</v>
       </c>
-      <c r="B29" s="3"/>
-      <c r="C29" s="4"/>
-      <c r="D29" s="1"/>
+      <c r="B29" s="3">
+        <v>45588</v>
+      </c>
+      <c r="C29" s="4">
+        <v>100</v>
+      </c>
+      <c r="D29" s="1">
+        <v>1</v>
+      </c>
       <c r="E29" s="1">
         <v>57</v>
       </c>
@@ -1685,9 +1763,15 @@
       <c r="A30" s="1">
         <v>28</v>
       </c>
-      <c r="B30" s="3"/>
-      <c r="C30" s="4"/>
-      <c r="D30" s="1"/>
+      <c r="B30" s="3">
+        <v>45591</v>
+      </c>
+      <c r="C30" s="4">
+        <v>100</v>
+      </c>
+      <c r="D30" s="1">
+        <v>1</v>
+      </c>
       <c r="E30" s="1">
         <v>58</v>
       </c>
@@ -1711,9 +1795,15 @@
       <c r="A31" s="1">
         <v>29</v>
       </c>
-      <c r="B31" s="3"/>
-      <c r="C31" s="4"/>
-      <c r="D31" s="1"/>
+      <c r="B31" s="3">
+        <v>45591</v>
+      </c>
+      <c r="C31" s="4">
+        <v>100</v>
+      </c>
+      <c r="D31" s="1">
+        <v>1</v>
+      </c>
       <c r="E31" s="1">
         <v>59</v>
       </c>
@@ -1737,9 +1827,15 @@
       <c r="A32" s="1">
         <v>30</v>
       </c>
-      <c r="B32" s="3"/>
-      <c r="C32" s="4"/>
-      <c r="D32" s="1"/>
+      <c r="B32" s="3">
+        <v>45591</v>
+      </c>
+      <c r="C32" s="4">
+        <v>100</v>
+      </c>
+      <c r="D32" s="1">
+        <v>1</v>
+      </c>
       <c r="E32" s="1">
         <v>60</v>
       </c>

--- a/LoanOfficer-A/2023/63 ibeyaima.xlsx
+++ b/LoanOfficer-A/2023/63 ibeyaima.xlsx
@@ -801,7 +801,7 @@
       </c>
       <c r="K1" s="10">
         <f>G1-K2</f>
-        <v>82</v>
+        <v>54</v>
       </c>
       <c r="L1" s="6"/>
       <c r="M1" s="5"/>
@@ -810,7 +810,7 @@
       </c>
       <c r="O1" s="8">
         <f>SUM(C3:C32)+SUM(G3:G32)+SUM(K3:K32)+SUM(O3:O32)</f>
-        <v>3800</v>
+        <v>6600</v>
       </c>
       <c r="P1" s="6"/>
     </row>
@@ -834,7 +834,7 @@
       </c>
       <c r="K2" s="9">
         <f>SUM(D3:D32)+SUM(H3:H32)+SUM(L3:L32)+SUM(P3:P32)</f>
-        <v>38</v>
+        <v>66</v>
       </c>
       <c r="L2" s="6"/>
       <c r="M2" s="5"/>
@@ -843,7 +843,7 @@
       </c>
       <c r="O2" s="11">
         <f>C2-O1</f>
-        <v>8200</v>
+        <v>5400</v>
       </c>
       <c r="P2" s="6"/>
     </row>
@@ -875,9 +875,15 @@
       <c r="I3" s="1">
         <v>61</v>
       </c>
-      <c r="J3" s="3"/>
-      <c r="K3" s="4"/>
-      <c r="L3" s="1"/>
+      <c r="J3" s="3">
+        <v>45621</v>
+      </c>
+      <c r="K3" s="4">
+        <v>100</v>
+      </c>
+      <c r="L3" s="1">
+        <v>1</v>
+      </c>
       <c r="M3" s="1">
         <v>91</v>
       </c>
@@ -913,9 +919,15 @@
       <c r="I4" s="1">
         <v>62</v>
       </c>
-      <c r="J4" s="3"/>
-      <c r="K4" s="4"/>
-      <c r="L4" s="1"/>
+      <c r="J4" s="3">
+        <v>45621</v>
+      </c>
+      <c r="K4" s="4">
+        <v>100</v>
+      </c>
+      <c r="L4" s="1">
+        <v>1</v>
+      </c>
       <c r="M4" s="1">
         <v>92</v>
       </c>
@@ -951,9 +963,15 @@
       <c r="I5" s="1">
         <v>63</v>
       </c>
-      <c r="J5" s="3"/>
-      <c r="K5" s="4"/>
-      <c r="L5" s="1"/>
+      <c r="J5" s="3">
+        <v>45621</v>
+      </c>
+      <c r="K5" s="4">
+        <v>100</v>
+      </c>
+      <c r="L5" s="1">
+        <v>1</v>
+      </c>
       <c r="M5" s="1">
         <v>93</v>
       </c>
@@ -989,9 +1007,15 @@
       <c r="I6" s="1">
         <v>64</v>
       </c>
-      <c r="J6" s="3"/>
-      <c r="K6" s="4"/>
-      <c r="L6" s="1"/>
+      <c r="J6" s="3">
+        <v>45621</v>
+      </c>
+      <c r="K6" s="4">
+        <v>100</v>
+      </c>
+      <c r="L6" s="1">
+        <v>1</v>
+      </c>
       <c r="M6" s="1">
         <v>94</v>
       </c>
@@ -1027,9 +1051,15 @@
       <c r="I7" s="1">
         <v>65</v>
       </c>
-      <c r="J7" s="3"/>
-      <c r="K7" s="4"/>
-      <c r="L7" s="1"/>
+      <c r="J7" s="3">
+        <v>45621</v>
+      </c>
+      <c r="K7" s="4">
+        <v>100</v>
+      </c>
+      <c r="L7" s="1">
+        <v>1</v>
+      </c>
       <c r="M7" s="1">
         <v>95</v>
       </c>
@@ -1065,9 +1095,15 @@
       <c r="I8" s="1">
         <v>66</v>
       </c>
-      <c r="J8" s="3"/>
-      <c r="K8" s="4"/>
-      <c r="L8" s="1"/>
+      <c r="J8" s="3">
+        <v>45621</v>
+      </c>
+      <c r="K8" s="4">
+        <v>100</v>
+      </c>
+      <c r="L8" s="1">
+        <v>1</v>
+      </c>
       <c r="M8" s="1">
         <v>96</v>
       </c>
@@ -1167,9 +1203,15 @@
       <c r="E11" s="1">
         <v>39</v>
       </c>
-      <c r="F11" s="3"/>
-      <c r="G11" s="4"/>
-      <c r="H11" s="1"/>
+      <c r="F11" s="3">
+        <v>45603</v>
+      </c>
+      <c r="G11" s="4">
+        <v>100</v>
+      </c>
+      <c r="H11" s="1">
+        <v>1</v>
+      </c>
       <c r="I11" s="1">
         <v>69</v>
       </c>
@@ -1199,9 +1241,15 @@
       <c r="E12" s="1">
         <v>40</v>
       </c>
-      <c r="F12" s="3"/>
-      <c r="G12" s="4"/>
-      <c r="H12" s="1"/>
+      <c r="F12" s="3">
+        <v>45606</v>
+      </c>
+      <c r="G12" s="4">
+        <v>100</v>
+      </c>
+      <c r="H12" s="1">
+        <v>1</v>
+      </c>
       <c r="I12" s="1">
         <v>70</v>
       </c>
@@ -1231,9 +1279,15 @@
       <c r="E13" s="1">
         <v>41</v>
       </c>
-      <c r="F13" s="3"/>
-      <c r="G13" s="4"/>
-      <c r="H13" s="1"/>
+      <c r="F13" s="3">
+        <v>45606</v>
+      </c>
+      <c r="G13" s="4">
+        <v>100</v>
+      </c>
+      <c r="H13" s="1">
+        <v>1</v>
+      </c>
       <c r="I13" s="1">
         <v>71</v>
       </c>
@@ -1263,9 +1317,15 @@
       <c r="E14" s="1">
         <v>42</v>
       </c>
-      <c r="F14" s="3"/>
-      <c r="G14" s="4"/>
-      <c r="H14" s="1"/>
+      <c r="F14" s="3">
+        <v>45608</v>
+      </c>
+      <c r="G14" s="4">
+        <v>100</v>
+      </c>
+      <c r="H14" s="1">
+        <v>1</v>
+      </c>
       <c r="I14" s="1">
         <v>72</v>
       </c>
@@ -1295,9 +1355,15 @@
       <c r="E15" s="1">
         <v>43</v>
       </c>
-      <c r="F15" s="3"/>
-      <c r="G15" s="4"/>
-      <c r="H15" s="1"/>
+      <c r="F15" s="3">
+        <v>45608</v>
+      </c>
+      <c r="G15" s="4">
+        <v>100</v>
+      </c>
+      <c r="H15" s="1">
+        <v>1</v>
+      </c>
       <c r="I15" s="1">
         <v>73</v>
       </c>
@@ -1327,9 +1393,15 @@
       <c r="E16" s="1">
         <v>44</v>
       </c>
-      <c r="F16" s="3"/>
-      <c r="G16" s="4"/>
-      <c r="H16" s="1"/>
+      <c r="F16" s="3">
+        <v>45608</v>
+      </c>
+      <c r="G16" s="4">
+        <v>100</v>
+      </c>
+      <c r="H16" s="1">
+        <v>1</v>
+      </c>
       <c r="I16" s="1">
         <v>74</v>
       </c>
@@ -1359,9 +1431,15 @@
       <c r="E17" s="1">
         <v>45</v>
       </c>
-      <c r="F17" s="3"/>
-      <c r="G17" s="4"/>
-      <c r="H17" s="1"/>
+      <c r="F17" s="3">
+        <v>45609</v>
+      </c>
+      <c r="G17" s="4">
+        <v>100</v>
+      </c>
+      <c r="H17" s="1">
+        <v>1</v>
+      </c>
       <c r="I17" s="1">
         <v>75</v>
       </c>
@@ -1391,9 +1469,15 @@
       <c r="E18" s="1">
         <v>46</v>
       </c>
-      <c r="F18" s="3"/>
-      <c r="G18" s="4"/>
-      <c r="H18" s="1"/>
+      <c r="F18" s="3">
+        <v>45610</v>
+      </c>
+      <c r="G18" s="4">
+        <v>100</v>
+      </c>
+      <c r="H18" s="1">
+        <v>1</v>
+      </c>
       <c r="I18" s="1">
         <v>76</v>
       </c>
@@ -1423,9 +1507,15 @@
       <c r="E19" s="1">
         <v>47</v>
       </c>
-      <c r="F19" s="3"/>
-      <c r="G19" s="4"/>
-      <c r="H19" s="1"/>
+      <c r="F19" s="3">
+        <v>45612</v>
+      </c>
+      <c r="G19" s="4">
+        <v>100</v>
+      </c>
+      <c r="H19" s="1">
+        <v>1</v>
+      </c>
       <c r="I19" s="1">
         <v>77</v>
       </c>
@@ -1455,9 +1545,15 @@
       <c r="E20" s="1">
         <v>48</v>
       </c>
-      <c r="F20" s="3"/>
-      <c r="G20" s="4"/>
-      <c r="H20" s="1"/>
+      <c r="F20" s="3">
+        <v>45612</v>
+      </c>
+      <c r="G20" s="4">
+        <v>100</v>
+      </c>
+      <c r="H20" s="1">
+        <v>1</v>
+      </c>
       <c r="I20" s="1">
         <v>78</v>
       </c>
@@ -1487,9 +1583,15 @@
       <c r="E21" s="1">
         <v>49</v>
       </c>
-      <c r="F21" s="3"/>
-      <c r="G21" s="4"/>
-      <c r="H21" s="1"/>
+      <c r="F21" s="3">
+        <v>45612</v>
+      </c>
+      <c r="G21" s="4">
+        <v>100</v>
+      </c>
+      <c r="H21" s="1">
+        <v>1</v>
+      </c>
       <c r="I21" s="1">
         <v>79</v>
       </c>
@@ -1519,9 +1621,15 @@
       <c r="E22" s="1">
         <v>50</v>
       </c>
-      <c r="F22" s="3"/>
-      <c r="G22" s="4"/>
-      <c r="H22" s="1"/>
+      <c r="F22" s="3">
+        <v>45615</v>
+      </c>
+      <c r="G22" s="4">
+        <v>100</v>
+      </c>
+      <c r="H22" s="1">
+        <v>1</v>
+      </c>
       <c r="I22" s="1">
         <v>80</v>
       </c>
@@ -1551,9 +1659,15 @@
       <c r="E23" s="1">
         <v>51</v>
       </c>
-      <c r="F23" s="3"/>
-      <c r="G23" s="4"/>
-      <c r="H23" s="1"/>
+      <c r="F23" s="3">
+        <v>45616</v>
+      </c>
+      <c r="G23" s="4">
+        <v>100</v>
+      </c>
+      <c r="H23" s="1">
+        <v>1</v>
+      </c>
       <c r="I23" s="1">
         <v>81</v>
       </c>
@@ -1583,9 +1697,15 @@
       <c r="E24" s="1">
         <v>52</v>
       </c>
-      <c r="F24" s="3"/>
-      <c r="G24" s="4"/>
-      <c r="H24" s="1"/>
+      <c r="F24" s="3">
+        <v>45617</v>
+      </c>
+      <c r="G24" s="4">
+        <v>100</v>
+      </c>
+      <c r="H24" s="1">
+        <v>1</v>
+      </c>
       <c r="I24" s="1">
         <v>82</v>
       </c>
@@ -1615,9 +1735,15 @@
       <c r="E25" s="1">
         <v>53</v>
       </c>
-      <c r="F25" s="3"/>
-      <c r="G25" s="4"/>
-      <c r="H25" s="1"/>
+      <c r="F25" s="3">
+        <v>45618</v>
+      </c>
+      <c r="G25" s="4">
+        <v>100</v>
+      </c>
+      <c r="H25" s="1">
+        <v>1</v>
+      </c>
       <c r="I25" s="1">
         <v>83</v>
       </c>
@@ -1647,9 +1773,15 @@
       <c r="E26" s="1">
         <v>54</v>
       </c>
-      <c r="F26" s="3"/>
-      <c r="G26" s="4"/>
-      <c r="H26" s="1"/>
+      <c r="F26" s="3">
+        <v>45619</v>
+      </c>
+      <c r="G26" s="4">
+        <v>100</v>
+      </c>
+      <c r="H26" s="1">
+        <v>1</v>
+      </c>
       <c r="I26" s="1">
         <v>84</v>
       </c>
@@ -1679,9 +1811,15 @@
       <c r="E27" s="1">
         <v>55</v>
       </c>
-      <c r="F27" s="3"/>
-      <c r="G27" s="4"/>
-      <c r="H27" s="1"/>
+      <c r="F27" s="3">
+        <v>45621</v>
+      </c>
+      <c r="G27" s="4">
+        <v>100</v>
+      </c>
+      <c r="H27" s="1">
+        <v>1</v>
+      </c>
       <c r="I27" s="1">
         <v>85</v>
       </c>
@@ -1711,9 +1849,15 @@
       <c r="E28" s="1">
         <v>56</v>
       </c>
-      <c r="F28" s="3"/>
-      <c r="G28" s="4"/>
-      <c r="H28" s="1"/>
+      <c r="F28" s="3">
+        <v>45621</v>
+      </c>
+      <c r="G28" s="4">
+        <v>100</v>
+      </c>
+      <c r="H28" s="1">
+        <v>1</v>
+      </c>
       <c r="I28" s="1">
         <v>86</v>
       </c>
@@ -1743,9 +1887,15 @@
       <c r="E29" s="1">
         <v>57</v>
       </c>
-      <c r="F29" s="3"/>
-      <c r="G29" s="4"/>
-      <c r="H29" s="1"/>
+      <c r="F29" s="3">
+        <v>45621</v>
+      </c>
+      <c r="G29" s="4">
+        <v>100</v>
+      </c>
+      <c r="H29" s="1">
+        <v>1</v>
+      </c>
       <c r="I29" s="1">
         <v>87</v>
       </c>
@@ -1775,9 +1925,15 @@
       <c r="E30" s="1">
         <v>58</v>
       </c>
-      <c r="F30" s="3"/>
-      <c r="G30" s="4"/>
-      <c r="H30" s="1"/>
+      <c r="F30" s="3">
+        <v>45621</v>
+      </c>
+      <c r="G30" s="4">
+        <v>100</v>
+      </c>
+      <c r="H30" s="1">
+        <v>1</v>
+      </c>
       <c r="I30" s="1">
         <v>88</v>
       </c>
@@ -1807,9 +1963,15 @@
       <c r="E31" s="1">
         <v>59</v>
       </c>
-      <c r="F31" s="3"/>
-      <c r="G31" s="4"/>
-      <c r="H31" s="1"/>
+      <c r="F31" s="3">
+        <v>45621</v>
+      </c>
+      <c r="G31" s="4">
+        <v>100</v>
+      </c>
+      <c r="H31" s="1">
+        <v>1</v>
+      </c>
       <c r="I31" s="1">
         <v>89</v>
       </c>
@@ -1839,9 +2001,15 @@
       <c r="E32" s="1">
         <v>60</v>
       </c>
-      <c r="F32" s="3"/>
-      <c r="G32" s="4"/>
-      <c r="H32" s="1"/>
+      <c r="F32" s="3">
+        <v>45621</v>
+      </c>
+      <c r="G32" s="4">
+        <v>100</v>
+      </c>
+      <c r="H32" s="1">
+        <v>1</v>
+      </c>
       <c r="I32" s="1">
         <v>90</v>
       </c>

--- a/LoanOfficer-A/2023/63 ibeyaima.xlsx
+++ b/LoanOfficer-A/2023/63 ibeyaima.xlsx
@@ -801,7 +801,7 @@
       </c>
       <c r="K1" s="10">
         <f>G1-K2</f>
-        <v>54</v>
+        <v>38</v>
       </c>
       <c r="L1" s="6"/>
       <c r="M1" s="5"/>
@@ -810,7 +810,7 @@
       </c>
       <c r="O1" s="8">
         <f>SUM(C3:C32)+SUM(G3:G32)+SUM(K3:K32)+SUM(O3:O32)</f>
-        <v>6600</v>
+        <v>8200</v>
       </c>
       <c r="P1" s="6"/>
     </row>
@@ -834,7 +834,7 @@
       </c>
       <c r="K2" s="9">
         <f>SUM(D3:D32)+SUM(H3:H32)+SUM(L3:L32)+SUM(P3:P32)</f>
-        <v>66</v>
+        <v>82</v>
       </c>
       <c r="L2" s="6"/>
       <c r="M2" s="5"/>
@@ -843,7 +843,7 @@
       </c>
       <c r="O2" s="11">
         <f>C2-O1</f>
-        <v>5400</v>
+        <v>3800</v>
       </c>
       <c r="P2" s="6"/>
     </row>
@@ -1139,9 +1139,15 @@
       <c r="I9" s="1">
         <v>67</v>
       </c>
-      <c r="J9" s="3"/>
-      <c r="K9" s="4"/>
-      <c r="L9" s="1"/>
+      <c r="J9" s="3">
+        <v>45622</v>
+      </c>
+      <c r="K9" s="4">
+        <v>100</v>
+      </c>
+      <c r="L9" s="1">
+        <v>1</v>
+      </c>
       <c r="M9" s="1">
         <v>97</v>
       </c>
@@ -1177,9 +1183,15 @@
       <c r="I10" s="1">
         <v>68</v>
       </c>
-      <c r="J10" s="3"/>
-      <c r="K10" s="4"/>
-      <c r="L10" s="1"/>
+      <c r="J10" s="3">
+        <v>45622</v>
+      </c>
+      <c r="K10" s="4">
+        <v>100</v>
+      </c>
+      <c r="L10" s="1">
+        <v>1</v>
+      </c>
       <c r="M10" s="1">
         <v>98</v>
       </c>
@@ -1215,9 +1227,15 @@
       <c r="I11" s="1">
         <v>69</v>
       </c>
-      <c r="J11" s="3"/>
-      <c r="K11" s="4"/>
-      <c r="L11" s="1"/>
+      <c r="J11" s="3">
+        <v>45622</v>
+      </c>
+      <c r="K11" s="4">
+        <v>100</v>
+      </c>
+      <c r="L11" s="1">
+        <v>1</v>
+      </c>
       <c r="M11" s="1">
         <v>99</v>
       </c>
@@ -1253,9 +1271,15 @@
       <c r="I12" s="1">
         <v>70</v>
       </c>
-      <c r="J12" s="3"/>
-      <c r="K12" s="4"/>
-      <c r="L12" s="1"/>
+      <c r="J12" s="3">
+        <v>45622</v>
+      </c>
+      <c r="K12" s="4">
+        <v>100</v>
+      </c>
+      <c r="L12" s="1">
+        <v>1</v>
+      </c>
       <c r="M12" s="1">
         <v>100</v>
       </c>
@@ -1291,9 +1315,15 @@
       <c r="I13" s="1">
         <v>71</v>
       </c>
-      <c r="J13" s="3"/>
-      <c r="K13" s="4"/>
-      <c r="L13" s="1"/>
+      <c r="J13" s="3">
+        <v>45622</v>
+      </c>
+      <c r="K13" s="4">
+        <v>100</v>
+      </c>
+      <c r="L13" s="1">
+        <v>1</v>
+      </c>
       <c r="M13" s="1">
         <v>101</v>
       </c>
@@ -1329,9 +1359,15 @@
       <c r="I14" s="1">
         <v>72</v>
       </c>
-      <c r="J14" s="3"/>
-      <c r="K14" s="4"/>
-      <c r="L14" s="1"/>
+      <c r="J14" s="3">
+        <v>45622</v>
+      </c>
+      <c r="K14" s="4">
+        <v>100</v>
+      </c>
+      <c r="L14" s="1">
+        <v>1</v>
+      </c>
       <c r="M14" s="1">
         <v>102</v>
       </c>
@@ -1367,9 +1403,15 @@
       <c r="I15" s="1">
         <v>73</v>
       </c>
-      <c r="J15" s="3"/>
-      <c r="K15" s="4"/>
-      <c r="L15" s="1"/>
+      <c r="J15" s="3">
+        <v>45622</v>
+      </c>
+      <c r="K15" s="4">
+        <v>100</v>
+      </c>
+      <c r="L15" s="1">
+        <v>1</v>
+      </c>
       <c r="M15" s="1">
         <v>103</v>
       </c>
@@ -1405,9 +1447,15 @@
       <c r="I16" s="1">
         <v>74</v>
       </c>
-      <c r="J16" s="3"/>
-      <c r="K16" s="4"/>
-      <c r="L16" s="1"/>
+      <c r="J16" s="3">
+        <v>45622</v>
+      </c>
+      <c r="K16" s="4">
+        <v>100</v>
+      </c>
+      <c r="L16" s="1">
+        <v>1</v>
+      </c>
       <c r="M16" s="1">
         <v>104</v>
       </c>
@@ -1443,9 +1491,15 @@
       <c r="I17" s="1">
         <v>75</v>
       </c>
-      <c r="J17" s="3"/>
-      <c r="K17" s="4"/>
-      <c r="L17" s="1"/>
+      <c r="J17" s="3">
+        <v>45622</v>
+      </c>
+      <c r="K17" s="4">
+        <v>100</v>
+      </c>
+      <c r="L17" s="1">
+        <v>1</v>
+      </c>
       <c r="M17" s="1">
         <v>105</v>
       </c>
@@ -1481,9 +1535,15 @@
       <c r="I18" s="1">
         <v>76</v>
       </c>
-      <c r="J18" s="3"/>
-      <c r="K18" s="4"/>
-      <c r="L18" s="1"/>
+      <c r="J18" s="3">
+        <v>45622</v>
+      </c>
+      <c r="K18" s="4">
+        <v>100</v>
+      </c>
+      <c r="L18" s="1">
+        <v>1</v>
+      </c>
       <c r="M18" s="1">
         <v>106</v>
       </c>
@@ -1519,9 +1579,15 @@
       <c r="I19" s="1">
         <v>77</v>
       </c>
-      <c r="J19" s="3"/>
-      <c r="K19" s="4"/>
-      <c r="L19" s="1"/>
+      <c r="J19" s="3">
+        <v>45622</v>
+      </c>
+      <c r="K19" s="4">
+        <v>100</v>
+      </c>
+      <c r="L19" s="1">
+        <v>1</v>
+      </c>
       <c r="M19" s="1">
         <v>107</v>
       </c>
@@ -1557,9 +1623,15 @@
       <c r="I20" s="1">
         <v>78</v>
       </c>
-      <c r="J20" s="3"/>
-      <c r="K20" s="4"/>
-      <c r="L20" s="1"/>
+      <c r="J20" s="3">
+        <v>45623</v>
+      </c>
+      <c r="K20" s="4">
+        <v>100</v>
+      </c>
+      <c r="L20" s="1">
+        <v>1</v>
+      </c>
       <c r="M20" s="1">
         <v>108</v>
       </c>
@@ -1595,9 +1667,15 @@
       <c r="I21" s="1">
         <v>79</v>
       </c>
-      <c r="J21" s="3"/>
-      <c r="K21" s="4"/>
-      <c r="L21" s="1"/>
+      <c r="J21" s="3">
+        <v>45624</v>
+      </c>
+      <c r="K21" s="4">
+        <v>100</v>
+      </c>
+      <c r="L21" s="1">
+        <v>1</v>
+      </c>
       <c r="M21" s="1">
         <v>109</v>
       </c>
@@ -1633,9 +1711,15 @@
       <c r="I22" s="1">
         <v>80</v>
       </c>
-      <c r="J22" s="3"/>
-      <c r="K22" s="4"/>
-      <c r="L22" s="1"/>
+      <c r="J22" s="3">
+        <v>45625</v>
+      </c>
+      <c r="K22" s="4">
+        <v>100</v>
+      </c>
+      <c r="L22" s="1">
+        <v>1</v>
+      </c>
       <c r="M22" s="1">
         <v>110</v>
       </c>
@@ -1671,9 +1755,15 @@
       <c r="I23" s="1">
         <v>81</v>
       </c>
-      <c r="J23" s="3"/>
-      <c r="K23" s="4"/>
-      <c r="L23" s="1"/>
+      <c r="J23" s="3">
+        <v>45626</v>
+      </c>
+      <c r="K23" s="4">
+        <v>100</v>
+      </c>
+      <c r="L23" s="1">
+        <v>1</v>
+      </c>
       <c r="M23" s="1">
         <v>111</v>
       </c>
@@ -1709,9 +1799,15 @@
       <c r="I24" s="1">
         <v>82</v>
       </c>
-      <c r="J24" s="3"/>
-      <c r="K24" s="4"/>
-      <c r="L24" s="1"/>
+      <c r="J24" s="3">
+        <v>45627</v>
+      </c>
+      <c r="K24" s="4">
+        <v>100</v>
+      </c>
+      <c r="L24" s="1">
+        <v>1</v>
+      </c>
       <c r="M24" s="1">
         <v>112</v>
       </c>

--- a/LoanOfficer-A/2023/63 ibeyaima.xlsx
+++ b/LoanOfficer-A/2023/63 ibeyaima.xlsx
@@ -801,7 +801,7 @@
       </c>
       <c r="K1" s="10">
         <f>G1-K2</f>
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="L1" s="6"/>
       <c r="M1" s="5"/>
@@ -810,7 +810,7 @@
       </c>
       <c r="O1" s="8">
         <f>SUM(C3:C32)+SUM(G3:G32)+SUM(K3:K32)+SUM(O3:O32)</f>
-        <v>8200</v>
+        <v>8800</v>
       </c>
       <c r="P1" s="6"/>
     </row>
@@ -834,7 +834,7 @@
       </c>
       <c r="K2" s="9">
         <f>SUM(D3:D32)+SUM(H3:H32)+SUM(L3:L32)+SUM(P3:P32)</f>
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="L2" s="6"/>
       <c r="M2" s="5"/>
@@ -843,7 +843,7 @@
       </c>
       <c r="O2" s="11">
         <f>C2-O1</f>
-        <v>3800</v>
+        <v>3200</v>
       </c>
       <c r="P2" s="6"/>
     </row>
@@ -1843,9 +1843,15 @@
       <c r="I25" s="1">
         <v>83</v>
       </c>
-      <c r="J25" s="3"/>
-      <c r="K25" s="4"/>
-      <c r="L25" s="1"/>
+      <c r="J25" s="3">
+        <v>45629</v>
+      </c>
+      <c r="K25" s="4">
+        <v>100</v>
+      </c>
+      <c r="L25" s="1">
+        <v>1</v>
+      </c>
       <c r="M25" s="1">
         <v>113</v>
       </c>
@@ -1881,9 +1887,15 @@
       <c r="I26" s="1">
         <v>84</v>
       </c>
-      <c r="J26" s="3"/>
-      <c r="K26" s="4"/>
-      <c r="L26" s="1"/>
+      <c r="J26" s="3">
+        <v>45629</v>
+      </c>
+      <c r="K26" s="4">
+        <v>100</v>
+      </c>
+      <c r="L26" s="1">
+        <v>1</v>
+      </c>
       <c r="M26" s="1">
         <v>114</v>
       </c>
@@ -1919,9 +1931,15 @@
       <c r="I27" s="1">
         <v>85</v>
       </c>
-      <c r="J27" s="3"/>
-      <c r="K27" s="4"/>
-      <c r="L27" s="1"/>
+      <c r="J27" s="3">
+        <v>45629</v>
+      </c>
+      <c r="K27" s="4">
+        <v>100</v>
+      </c>
+      <c r="L27" s="1">
+        <v>1</v>
+      </c>
       <c r="M27" s="1">
         <v>115</v>
       </c>
@@ -1957,9 +1975,15 @@
       <c r="I28" s="1">
         <v>86</v>
       </c>
-      <c r="J28" s="3"/>
-      <c r="K28" s="4"/>
-      <c r="L28" s="1"/>
+      <c r="J28" s="3">
+        <v>45632</v>
+      </c>
+      <c r="K28" s="4">
+        <v>100</v>
+      </c>
+      <c r="L28" s="1">
+        <v>1</v>
+      </c>
       <c r="M28" s="1">
         <v>116</v>
       </c>
@@ -1995,9 +2019,15 @@
       <c r="I29" s="1">
         <v>87</v>
       </c>
-      <c r="J29" s="3"/>
-      <c r="K29" s="4"/>
-      <c r="L29" s="1"/>
+      <c r="J29" s="3">
+        <v>45632</v>
+      </c>
+      <c r="K29" s="4">
+        <v>100</v>
+      </c>
+      <c r="L29" s="1">
+        <v>1</v>
+      </c>
       <c r="M29" s="1">
         <v>117</v>
       </c>
@@ -2033,9 +2063,15 @@
       <c r="I30" s="1">
         <v>88</v>
       </c>
-      <c r="J30" s="3"/>
-      <c r="K30" s="4"/>
-      <c r="L30" s="1"/>
+      <c r="J30" s="3">
+        <v>45632</v>
+      </c>
+      <c r="K30" s="4">
+        <v>100</v>
+      </c>
+      <c r="L30" s="1">
+        <v>1</v>
+      </c>
       <c r="M30" s="1">
         <v>118</v>
       </c>

--- a/LoanOfficer-A/2023/63 ibeyaima.xlsx
+++ b/LoanOfficer-A/2023/63 ibeyaima.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
   <si>
     <t xml:space="preserve">Loan Amount: </t>
   </si>
@@ -95,6 +95,9 @@
   </si>
   <si>
     <t>TEACHER</t>
+  </si>
+  <si>
+    <t>Date of completion</t>
   </si>
 </sst>
 </file>
@@ -210,7 +213,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -271,6 +274,9 @@
     </xf>
     <xf numFmtId="15" fontId="6" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -617,8 +623,8 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B2" s="21"/>
-      <c r="C2" s="21"/>
+      <c r="B2" s="22"/>
+      <c r="C2" s="22"/>
     </row>
     <row r="5" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B5" s="13"/>
@@ -693,20 +699,20 @@
       <c r="C16" s="14"/>
     </row>
     <row r="17" spans="2:3" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="B17" s="22" t="s">
+      <c r="B17" s="23" t="s">
         <v>16</v>
       </c>
-      <c r="C17" s="22"/>
+      <c r="C17" s="23"/>
     </row>
     <row r="19" spans="2:3" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B19" s="17"/>
       <c r="C19" s="17"/>
     </row>
     <row r="21" spans="2:3" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="B21" s="22" t="s">
+      <c r="B21" s="23" t="s">
         <v>17</v>
       </c>
-      <c r="C21" s="22"/>
+      <c r="C21" s="23"/>
     </row>
     <row r="22" spans="2:3" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B22" s="14"/>
@@ -801,7 +807,7 @@
       </c>
       <c r="K1" s="10">
         <f>G1-K2</f>
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="L1" s="6"/>
       <c r="M1" s="5"/>
@@ -810,7 +816,7 @@
       </c>
       <c r="O1" s="8">
         <f>SUM(C3:C32)+SUM(G3:G32)+SUM(K3:K32)+SUM(O3:O32)</f>
-        <v>8800</v>
+        <v>9600</v>
       </c>
       <c r="P1" s="6"/>
     </row>
@@ -825,8 +831,13 @@
       </c>
       <c r="D2" s="6"/>
       <c r="E2" s="5"/>
-      <c r="F2" s="5"/>
-      <c r="G2" s="7"/>
+      <c r="F2" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="G2" s="21">
+        <f>B3+G1-1</f>
+        <v>45680</v>
+      </c>
       <c r="H2" s="6"/>
       <c r="I2" s="6"/>
       <c r="J2" s="7" t="s">
@@ -834,7 +845,7 @@
       </c>
       <c r="K2" s="9">
         <f>SUM(D3:D32)+SUM(H3:H32)+SUM(L3:L32)+SUM(P3:P32)</f>
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="L2" s="6"/>
       <c r="M2" s="5"/>
@@ -843,7 +854,7 @@
       </c>
       <c r="O2" s="11">
         <f>C2-O1</f>
-        <v>3200</v>
+        <v>2400</v>
       </c>
       <c r="P2" s="6"/>
     </row>
@@ -887,9 +898,15 @@
       <c r="M3" s="1">
         <v>91</v>
       </c>
-      <c r="N3" s="3"/>
-      <c r="O3" s="4"/>
-      <c r="P3" s="1"/>
+      <c r="N3" s="3">
+        <v>45637</v>
+      </c>
+      <c r="O3" s="4">
+        <v>100</v>
+      </c>
+      <c r="P3" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="4" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
@@ -931,9 +948,15 @@
       <c r="M4" s="1">
         <v>92</v>
       </c>
-      <c r="N4" s="3"/>
-      <c r="O4" s="4"/>
-      <c r="P4" s="1"/>
+      <c r="N4" s="3">
+        <v>45639</v>
+      </c>
+      <c r="O4" s="4">
+        <v>100</v>
+      </c>
+      <c r="P4" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="5" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
@@ -975,9 +998,15 @@
       <c r="M5" s="1">
         <v>93</v>
       </c>
-      <c r="N5" s="3"/>
-      <c r="O5" s="4"/>
-      <c r="P5" s="1"/>
+      <c r="N5" s="3">
+        <v>45642</v>
+      </c>
+      <c r="O5" s="4">
+        <v>100</v>
+      </c>
+      <c r="P5" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="6" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
@@ -1019,9 +1048,15 @@
       <c r="M6" s="1">
         <v>94</v>
       </c>
-      <c r="N6" s="3"/>
-      <c r="O6" s="4"/>
-      <c r="P6" s="1"/>
+      <c r="N6" s="3">
+        <v>45644</v>
+      </c>
+      <c r="O6" s="4">
+        <v>100</v>
+      </c>
+      <c r="P6" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="7" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
@@ -1063,9 +1098,15 @@
       <c r="M7" s="1">
         <v>95</v>
       </c>
-      <c r="N7" s="3"/>
-      <c r="O7" s="4"/>
-      <c r="P7" s="1"/>
+      <c r="N7" s="3">
+        <v>45646</v>
+      </c>
+      <c r="O7" s="4">
+        <v>100</v>
+      </c>
+      <c r="P7" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="8" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
@@ -1107,9 +1148,15 @@
       <c r="M8" s="1">
         <v>96</v>
       </c>
-      <c r="N8" s="3"/>
-      <c r="O8" s="4"/>
-      <c r="P8" s="1"/>
+      <c r="N8" s="3">
+        <v>45648</v>
+      </c>
+      <c r="O8" s="4">
+        <v>100</v>
+      </c>
+      <c r="P8" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="9" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
@@ -2107,9 +2154,15 @@
       <c r="I31" s="1">
         <v>89</v>
       </c>
-      <c r="J31" s="3"/>
-      <c r="K31" s="4"/>
-      <c r="L31" s="1"/>
+      <c r="J31" s="3">
+        <v>45633</v>
+      </c>
+      <c r="K31" s="4">
+        <v>100</v>
+      </c>
+      <c r="L31" s="1">
+        <v>1</v>
+      </c>
       <c r="M31" s="1">
         <v>119</v>
       </c>
@@ -2145,9 +2198,15 @@
       <c r="I32" s="1">
         <v>90</v>
       </c>
-      <c r="J32" s="3"/>
-      <c r="K32" s="4"/>
-      <c r="L32" s="1"/>
+      <c r="J32" s="3">
+        <v>45634</v>
+      </c>
+      <c r="K32" s="4">
+        <v>100</v>
+      </c>
+      <c r="L32" s="1">
+        <v>1</v>
+      </c>
       <c r="M32" s="1">
         <v>120</v>
       </c>

--- a/LoanOfficer-A/2023/63 ibeyaima.xlsx
+++ b/LoanOfficer-A/2023/63 ibeyaima.xlsx
@@ -605,7 +605,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -807,7 +807,7 @@
       </c>
       <c r="K1" s="10">
         <f>G1-K2</f>
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="L1" s="6"/>
       <c r="M1" s="5"/>
@@ -816,7 +816,7 @@
       </c>
       <c r="O1" s="8">
         <f>SUM(C3:C32)+SUM(G3:G32)+SUM(K3:K32)+SUM(O3:O32)</f>
-        <v>9600</v>
+        <v>10100</v>
       </c>
       <c r="P1" s="6"/>
     </row>
@@ -845,7 +845,7 @@
       </c>
       <c r="K2" s="9">
         <f>SUM(D3:D32)+SUM(H3:H32)+SUM(L3:L32)+SUM(P3:P32)</f>
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="L2" s="6"/>
       <c r="M2" s="5"/>
@@ -854,7 +854,7 @@
       </c>
       <c r="O2" s="11">
         <f>C2-O1</f>
-        <v>2400</v>
+        <v>1900</v>
       </c>
       <c r="P2" s="6"/>
     </row>
@@ -1198,9 +1198,15 @@
       <c r="M9" s="1">
         <v>97</v>
       </c>
-      <c r="N9" s="3"/>
-      <c r="O9" s="4"/>
-      <c r="P9" s="1"/>
+      <c r="N9" s="3">
+        <v>45650</v>
+      </c>
+      <c r="O9" s="4">
+        <v>100</v>
+      </c>
+      <c r="P9" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="10" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
@@ -1242,9 +1248,15 @@
       <c r="M10" s="1">
         <v>98</v>
       </c>
-      <c r="N10" s="3"/>
-      <c r="O10" s="4"/>
-      <c r="P10" s="1"/>
+      <c r="N10" s="3">
+        <v>45650</v>
+      </c>
+      <c r="O10" s="4">
+        <v>100</v>
+      </c>
+      <c r="P10" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="11" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
@@ -1286,9 +1298,15 @@
       <c r="M11" s="1">
         <v>99</v>
       </c>
-      <c r="N11" s="3"/>
-      <c r="O11" s="4"/>
-      <c r="P11" s="1"/>
+      <c r="N11" s="3">
+        <v>45650</v>
+      </c>
+      <c r="O11" s="4">
+        <v>100</v>
+      </c>
+      <c r="P11" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="12" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
@@ -1330,9 +1348,15 @@
       <c r="M12" s="1">
         <v>100</v>
       </c>
-      <c r="N12" s="3"/>
-      <c r="O12" s="4"/>
-      <c r="P12" s="1"/>
+      <c r="N12" s="3">
+        <v>45651</v>
+      </c>
+      <c r="O12" s="4">
+        <v>100</v>
+      </c>
+      <c r="P12" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="13" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
@@ -1374,9 +1398,15 @@
       <c r="M13" s="1">
         <v>101</v>
       </c>
-      <c r="N13" s="3"/>
-      <c r="O13" s="4"/>
-      <c r="P13" s="1"/>
+      <c r="N13" s="3">
+        <v>45654</v>
+      </c>
+      <c r="O13" s="4">
+        <v>100</v>
+      </c>
+      <c r="P13" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="14" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="1">

--- a/LoanOfficer-A/2023/63 ibeyaima.xlsx
+++ b/LoanOfficer-A/2023/63 ibeyaima.xlsx
@@ -605,7 +605,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -807,7 +807,7 @@
       </c>
       <c r="K1" s="10">
         <f>G1-K2</f>
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="L1" s="6"/>
       <c r="M1" s="5"/>
@@ -816,7 +816,7 @@
       </c>
       <c r="O1" s="8">
         <f>SUM(C3:C32)+SUM(G3:G32)+SUM(K3:K32)+SUM(O3:O32)</f>
-        <v>10100</v>
+        <v>10400</v>
       </c>
       <c r="P1" s="6"/>
     </row>
@@ -845,7 +845,7 @@
       </c>
       <c r="K2" s="9">
         <f>SUM(D3:D32)+SUM(H3:H32)+SUM(L3:L32)+SUM(P3:P32)</f>
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="L2" s="6"/>
       <c r="M2" s="5"/>
@@ -854,7 +854,7 @@
       </c>
       <c r="O2" s="11">
         <f>C2-O1</f>
-        <v>1900</v>
+        <v>1600</v>
       </c>
       <c r="P2" s="6"/>
     </row>
@@ -1448,9 +1448,15 @@
       <c r="M14" s="1">
         <v>102</v>
       </c>
-      <c r="N14" s="3"/>
-      <c r="O14" s="4"/>
-      <c r="P14" s="1"/>
+      <c r="N14" s="3">
+        <v>45655</v>
+      </c>
+      <c r="O14" s="4">
+        <v>100</v>
+      </c>
+      <c r="P14" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="15" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
@@ -1492,9 +1498,15 @@
       <c r="M15" s="1">
         <v>103</v>
       </c>
-      <c r="N15" s="3"/>
-      <c r="O15" s="4"/>
-      <c r="P15" s="1"/>
+      <c r="N15" s="3">
+        <v>45658</v>
+      </c>
+      <c r="O15" s="4">
+        <v>100</v>
+      </c>
+      <c r="P15" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="16" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
@@ -1536,9 +1548,15 @@
       <c r="M16" s="1">
         <v>104</v>
       </c>
-      <c r="N16" s="3"/>
-      <c r="O16" s="4"/>
-      <c r="P16" s="1"/>
+      <c r="N16" s="3">
+        <v>45660</v>
+      </c>
+      <c r="O16" s="4">
+        <v>100</v>
+      </c>
+      <c r="P16" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="17" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="1">

--- a/LoanOfficer-A/2023/63 ibeyaima.xlsx
+++ b/LoanOfficer-A/2023/63 ibeyaima.xlsx
@@ -605,7 +605,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -807,7 +807,7 @@
       </c>
       <c r="K1" s="10">
         <f>G1-K2</f>
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="L1" s="6"/>
       <c r="M1" s="5"/>
@@ -816,7 +816,7 @@
       </c>
       <c r="O1" s="8">
         <f>SUM(C3:C32)+SUM(G3:G32)+SUM(K3:K32)+SUM(O3:O32)</f>
-        <v>10400</v>
+        <v>10600</v>
       </c>
       <c r="P1" s="6"/>
     </row>
@@ -845,7 +845,7 @@
       </c>
       <c r="K2" s="9">
         <f>SUM(D3:D32)+SUM(H3:H32)+SUM(L3:L32)+SUM(P3:P32)</f>
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="L2" s="6"/>
       <c r="M2" s="5"/>
@@ -854,7 +854,7 @@
       </c>
       <c r="O2" s="11">
         <f>C2-O1</f>
-        <v>1600</v>
+        <v>1400</v>
       </c>
       <c r="P2" s="6"/>
     </row>
@@ -1598,9 +1598,15 @@
       <c r="M17" s="1">
         <v>105</v>
       </c>
-      <c r="N17" s="3"/>
-      <c r="O17" s="4"/>
-      <c r="P17" s="1"/>
+      <c r="N17" s="3">
+        <v>45669</v>
+      </c>
+      <c r="O17" s="4">
+        <v>100</v>
+      </c>
+      <c r="P17" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="18" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
@@ -1642,9 +1648,15 @@
       <c r="M18" s="1">
         <v>106</v>
       </c>
-      <c r="N18" s="3"/>
-      <c r="O18" s="4"/>
-      <c r="P18" s="1"/>
+      <c r="N18" s="3">
+        <v>45669</v>
+      </c>
+      <c r="O18" s="4">
+        <v>100</v>
+      </c>
+      <c r="P18" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="19" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="1">

--- a/LoanOfficer-A/2023/63 ibeyaima.xlsx
+++ b/LoanOfficer-A/2023/63 ibeyaima.xlsx
@@ -605,7 +605,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -807,7 +807,7 @@
       </c>
       <c r="K1" s="10">
         <f>G1-K2</f>
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L1" s="6"/>
       <c r="M1" s="5"/>
@@ -816,7 +816,7 @@
       </c>
       <c r="O1" s="8">
         <f>SUM(C3:C32)+SUM(G3:G32)+SUM(K3:K32)+SUM(O3:O32)</f>
-        <v>10600</v>
+        <v>10700</v>
       </c>
       <c r="P1" s="6"/>
     </row>
@@ -845,7 +845,7 @@
       </c>
       <c r="K2" s="9">
         <f>SUM(D3:D32)+SUM(H3:H32)+SUM(L3:L32)+SUM(P3:P32)</f>
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="L2" s="6"/>
       <c r="M2" s="5"/>
@@ -854,7 +854,7 @@
       </c>
       <c r="O2" s="11">
         <f>C2-O1</f>
-        <v>1400</v>
+        <v>1300</v>
       </c>
       <c r="P2" s="6"/>
     </row>
@@ -1698,9 +1698,15 @@
       <c r="M19" s="1">
         <v>107</v>
       </c>
-      <c r="N19" s="3"/>
-      <c r="O19" s="4"/>
-      <c r="P19" s="1"/>
+      <c r="N19" s="3">
+        <v>45689</v>
+      </c>
+      <c r="O19" s="4">
+        <v>100</v>
+      </c>
+      <c r="P19" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="20" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="1">

--- a/LoanOfficer-A/2023/63 ibeyaima.xlsx
+++ b/LoanOfficer-A/2023/63 ibeyaima.xlsx
@@ -807,7 +807,7 @@
       </c>
       <c r="K1" s="10">
         <f>G1-K2</f>
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="L1" s="6"/>
       <c r="M1" s="5"/>
@@ -816,7 +816,7 @@
       </c>
       <c r="O1" s="8">
         <f>SUM(C3:C32)+SUM(G3:G32)+SUM(K3:K32)+SUM(O3:O32)</f>
-        <v>10700</v>
+        <v>11100</v>
       </c>
       <c r="P1" s="6"/>
     </row>
@@ -845,7 +845,7 @@
       </c>
       <c r="K2" s="9">
         <f>SUM(D3:D32)+SUM(H3:H32)+SUM(L3:L32)+SUM(P3:P32)</f>
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="L2" s="6"/>
       <c r="M2" s="5"/>
@@ -854,7 +854,7 @@
       </c>
       <c r="O2" s="11">
         <f>C2-O1</f>
-        <v>1300</v>
+        <v>900</v>
       </c>
       <c r="P2" s="6"/>
     </row>
@@ -1748,9 +1748,15 @@
       <c r="M20" s="1">
         <v>108</v>
       </c>
-      <c r="N20" s="3"/>
-      <c r="O20" s="4"/>
-      <c r="P20" s="1"/>
+      <c r="N20" s="3">
+        <v>45697</v>
+      </c>
+      <c r="O20" s="4">
+        <v>100</v>
+      </c>
+      <c r="P20" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="21" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
@@ -1792,9 +1798,15 @@
       <c r="M21" s="1">
         <v>109</v>
       </c>
-      <c r="N21" s="3"/>
-      <c r="O21" s="4"/>
-      <c r="P21" s="1"/>
+      <c r="N21" s="3">
+        <v>45697</v>
+      </c>
+      <c r="O21" s="4">
+        <v>100</v>
+      </c>
+      <c r="P21" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="22" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
@@ -1836,9 +1848,15 @@
       <c r="M22" s="1">
         <v>110</v>
       </c>
-      <c r="N22" s="3"/>
-      <c r="O22" s="4"/>
-      <c r="P22" s="1"/>
+      <c r="N22" s="3">
+        <v>45699</v>
+      </c>
+      <c r="O22" s="4">
+        <v>100</v>
+      </c>
+      <c r="P22" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="23" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
@@ -1880,9 +1898,15 @@
       <c r="M23" s="1">
         <v>111</v>
       </c>
-      <c r="N23" s="3"/>
-      <c r="O23" s="4"/>
-      <c r="P23" s="1"/>
+      <c r="N23" s="3">
+        <v>45699</v>
+      </c>
+      <c r="O23" s="4">
+        <v>100</v>
+      </c>
+      <c r="P23" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="24" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="1">

--- a/LoanOfficer-A/2023/63 ibeyaima.xlsx
+++ b/LoanOfficer-A/2023/63 ibeyaima.xlsx
@@ -807,7 +807,7 @@
       </c>
       <c r="K1" s="10">
         <f>G1-K2</f>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="L1" s="6"/>
       <c r="M1" s="5"/>
@@ -816,7 +816,7 @@
       </c>
       <c r="O1" s="8">
         <f>SUM(C3:C32)+SUM(G3:G32)+SUM(K3:K32)+SUM(O3:O32)</f>
-        <v>11100</v>
+        <v>11200</v>
       </c>
       <c r="P1" s="6"/>
     </row>
@@ -845,7 +845,7 @@
       </c>
       <c r="K2" s="9">
         <f>SUM(D3:D32)+SUM(H3:H32)+SUM(L3:L32)+SUM(P3:P32)</f>
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="L2" s="6"/>
       <c r="M2" s="5"/>
@@ -854,7 +854,7 @@
       </c>
       <c r="O2" s="11">
         <f>C2-O1</f>
-        <v>900</v>
+        <v>800</v>
       </c>
       <c r="P2" s="6"/>
     </row>
@@ -1948,9 +1948,15 @@
       <c r="M24" s="1">
         <v>112</v>
       </c>
-      <c r="N24" s="3"/>
-      <c r="O24" s="4"/>
-      <c r="P24" s="1"/>
+      <c r="N24" s="3">
+        <v>45703</v>
+      </c>
+      <c r="O24" s="4">
+        <v>100</v>
+      </c>
+      <c r="P24" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="25" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
